--- a/詳細設計/00_詳細設計成果物一覧.xlsx
+++ b/詳細設計/00_詳細設計成果物一覧.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R60948e034c714f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R104b8abebeb9445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分冊方針・集計" sheetId="3" r:id="Ra1615cf00b674355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_成果物一覧" sheetId="4" r:id="Ra4c591d250ce4b8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_基本設計変更" sheetId="5" r:id="R19c0c74b47854164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9aaf570eeb7641fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R75bd201b264247f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分冊方針・集計" sheetId="3" r:id="R733fc66722df4f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_成果物一覧" sheetId="4" r:id="R7a418019c2134df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_基本設計変更" sheetId="5" r:id="R840d330ca43345d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -803,7 +803,7 @@
         <x:v>文書番号</x:v>
       </x:c>
       <x:c r="F15" s="19" t="str">
-        <x:v>Ver.1.1</x:v>
+        <x:v>Ver.1.2</x:v>
       </x:c>
       <x:c r="G15" s="19" t="str">
         <x:v>CW-DD-MGT-001</x:v>
@@ -826,7 +826,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="F16" s="19" t="str">
-        <x:v>2026-10-07</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="G16" s="19" t="str">
         <x:v>Ver.1.0</x:v>
@@ -1303,7 +1303,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>Ver.1.0</x:v>
+        <x:v>Ver.1.2</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
         <x:v>Ver.1.0</x:v>
@@ -1459,6 +1459,32 @@
       </x:c>
       <x:c r="H9" s="44" t="str">
         <x:v>作成済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="44" t="str">
+        <x:v>Ver.1.2</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C10" s="44" t="str">
+        <x:v>集計参照を現行Baselineに更新し、詳細設計への上流事項展開と根拠記載を明確化。</x:v>
+      </x:c>
+      <x:c r="D10" s="44" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E10" s="44" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F10" s="44" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H10" s="44" t="str">
+        <x:v>Review待ち</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1622,7 +1648,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>Ver.1.0</x:v>
+        <x:v>Ver.1.2</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
         <x:v>Ver.1.0</x:v>
@@ -1660,17 +1686,11 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>00_基本設計書総合管理.xlsx／現行Baseline</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="str">
-        <x:v>23_学員Reviewテスト管理/41</x:v>
-      </x:c>
-      <x:c r="E5" s="31" t="str">
-        <x:v>23_学員Reviewテスト管理/41</x:v>
-      </x:c>
-      <x:c r="F5" s="31" t="str">
-        <x:v>23_学員Reviewテスト管理/41</x:v>
-      </x:c>
+        <x:v>00_基本設計書総合管理.xlsx／BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="D5" s="31"/>
+      <x:c r="E5" s="31"/>
+      <x:c r="F5" s="31"/>
       <x:c r="G5" s="31" t="str">
         <x:v>23_学員Reviewテスト管理/41</x:v>
       </x:c>
@@ -1909,7 +1929,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="50" t="str">
-        <x:v>各分冊は基本設計参照、外部契約、正常/异常分岐、Data/SQL、权限、Transaction/排他、Log/Security、单体测试观点を含み、未定/TBDを残さない。Codingは詳細設計ID単位のBranch/PR、単体テストは同一ID単位の仕様書・証跡で追跡する。基本設計変更が必要な場合は修訂履歴と追跡表を更新し、Leader Review後にBaseline化する。</x:v>
+        <x:v>各分冊には、基本設計参照、外部契約、正常・異常分岐、Data／SQL、権限、Transaction／排他、Log／Security、単体テスト観点を対象機能に応じて具体的に記載し、未決事項を残さない。適用する基本設計の値・条件・規則を本文へ展開し、根拠は基本設計File名／Sheet名／設計ID又はCell位置で示す。Codingは詳細設計ID単位のBranch／PR、単体テストは同一ID単位の仕様書・証跡で追跡する。基本設計変更が必要な場合は改訂履歴と追跡表を更新し、Leader Review後にBaseline化する。</x:v>
       </x:c>
       <x:c r="B18" s="50" t="str">
         <x:v>各分冊は基本設計参照、外部契約、正常/异常分岐、Data/SQL、权限、Transaction/排他、Log/Security、单体测试观点を含み、未定/TBDを残さない。Codingは詳細設計ID単位のBranch/PR、単体テストは同一ID単位の仕様書・証跡で追跡する。基本設計変更が必要な場合は修訂履歴と追跡表を更新し、Leader Review後にBaseline化する。</x:v>
@@ -2374,7 +2394,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>Ver.1.1</x:v>
+        <x:v>Ver.1.2</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
         <x:v>Ver.1.0</x:v>
@@ -6065,7 +6085,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>Ver.1.0</x:v>
+        <x:v>Ver.1.2</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
         <x:v>Ver.1.0</x:v>
